--- a/reports/20260507/UI_BLOCK_UNBLOCK_FEEDBACK_STANDALONE_ADMIN_PW.xlsx
+++ b/reports/20260507/UI_BLOCK_UNBLOCK_FEEDBACK_STANDALONE_ADMIN_PW.xlsx
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -85,9 +85,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -455,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +482,7 @@
         </is>
       </c>
       <c r="J1" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K1" t="inlineStr">
         <is>
@@ -493,13 +490,13 @@
         </is>
       </c>
       <c r="L1" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11:26:50</t>
+          <t>16:05:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,14 +521,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11:26:54</t>
+          <t>16:06:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -556,14 +553,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>43.62s</t>
+          <t>69.24s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:27:02</t>
+          <t>16:06:05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -585,7 +582,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11:27:02</t>
+          <t>16:06:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -607,25 +604,771 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11:27:32</t>
+          <t>16:06:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Exception</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+          <t>Navigate to Interviews</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page.goto: Timeout 30000ms exceeded.
-Call log:
-  - navigating to "https://amsin.hirepro.in/crpo/#/agenticqa/interviews/", waiting until "networkidle"
-</t>
+          <t>Reached interviews page</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16:06:06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Select All Interviews</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Selecting 'All Interviews' from dropdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>16:06:16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Select All Interviews</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Selected 'All Interviews' view</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16:06:16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Filter Candidate</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Searching for candidate: Thridcandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>16:06:24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Filter Candidate</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Filtered for Thridcandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>16:06:24</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Click Elipsis</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Clicking on elipsis icon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>16:06:25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Click Elipsis</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Clicked elipsis icon</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>16:06:25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Action click on External Link Menu</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Clicking on View External Provide Feedback Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>16:06:26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Action click on External Link Menu</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Opened external link menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>16:06:26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Open External Link</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Opening external feedback link</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16:06:29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Open External Link</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Opened external feedback link</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16:06:29</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Close Modal</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closing the external link modal on main page</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16:06:29</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Close Modal</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed the external link modal successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16:06:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Validate Feedback Status</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Checking for 'Feedback is submitted.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16:06:30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Validate Feedback Status</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Found: Feedback is submitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16:06:30</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Block Feedback</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Blocking feedback with reason: This interview is not eligible for feedback on this platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16:06:38</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Block Feedback</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Blocked feedback successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16:06:43</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Verify Block Info</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Opening Blocked Feedback Info</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16:06:46</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Verify Block Info</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Opened blocked feedback info panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16:06:46</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Validate Block Info Content</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Validating block reason in UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16:06:46</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Validate Block Info Content</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Verified reason: This interview is not eligible for feedback on this platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16:06:46</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Close Info Panel</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closing the Blocked Feedback Info panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16:06:47</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Close Info Panel</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed info panel successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16:06:47</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Action click on External Link Menu</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Clicking on View External Provide Feedback Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16:06:47</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Action click on External Link Menu</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Opened external link menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16:06:47</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Verify External Link Blocked</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Opening external feedback link while blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16:06:49</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Validate FeedbackPage Content after Block</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Validating block reason on external page</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16:06:49</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Validate FeedbackPage Content after Block</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Verified block message on feedback page:This interview is not eligible for feedback on this platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16:06:49</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Close Modal</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closing the external link modal on main page</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>16:06:50</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Close Modal</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed the modal successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16:06:50</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unblock Feedback</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Unblocking feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16:06:52</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unblock Feedback</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Feedback unblocked successfully. Notifier: ×
+Un-Blocked successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16:06:59</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Verify Unblocked State</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Verifying the link is now unblocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16:07:02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Validate FeedbackPage Content after Unblock</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Feedback page: Validating block reason is gone</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16:07:02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Validate FeedbackPage Content after Unblock</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Verified block message is NOT present on feedback page</t>
         </is>
       </c>
     </row>

--- a/reports/20260507/UI_BLOCK_UNBLOCK_FEEDBACK_STANDALONE_ADMIN_PW.xlsx
+++ b/reports/20260507/UI_BLOCK_UNBLOCK_FEEDBACK_STANDALONE_ADMIN_PW.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16:05:59</t>
+          <t>12:55:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16:06:03</t>
+          <t>12:55:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -553,14 +553,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>69.24s</t>
+          <t>46.62s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16:06:05</t>
+          <t>12:55:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -582,7 +582,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16:06:05</t>
+          <t>12:55:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:06:05</t>
+          <t>12:55:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16:06:06</t>
+          <t>12:55:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16:06:16</t>
+          <t>12:55:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16:06:16</t>
+          <t>12:55:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -692,7 +692,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16:06:24</t>
+          <t>12:55:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16:06:24</t>
+          <t>12:55:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -736,7 +736,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16:06:25</t>
+          <t>12:55:46</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16:06:25</t>
+          <t>12:55:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16:06:26</t>
+          <t>12:55:46</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16:06:26</t>
+          <t>12:55:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16:06:29</t>
+          <t>12:55:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16:06:29</t>
+          <t>12:55:50</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -868,7 +868,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16:06:29</t>
+          <t>12:55:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16:06:30</t>
+          <t>12:55:50</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16:06:30</t>
+          <t>12:55:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16:06:30</t>
+          <t>12:55:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16:06:38</t>
+          <t>12:55:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16:06:43</t>
+          <t>12:55:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1000,7 +1000,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16:06:46</t>
+          <t>12:55:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1022,7 +1022,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16:06:46</t>
+          <t>12:55:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16:06:46</t>
+          <t>12:55:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16:06:46</t>
+          <t>12:55:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16:06:47</t>
+          <t>12:55:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1110,7 +1110,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16:06:47</t>
+          <t>12:55:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16:06:47</t>
+          <t>12:55:58</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16:06:47</t>
+          <t>12:55:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16:06:49</t>
+          <t>12:55:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16:06:49</t>
+          <t>12:55:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1220,7 +1220,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>16:06:49</t>
+          <t>12:55:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1242,7 +1242,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16:06:50</t>
+          <t>12:56:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1264,7 +1264,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16:06:50</t>
+          <t>12:56:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1286,7 +1286,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16:06:52</t>
+          <t>12:56:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16:06:59</t>
+          <t>12:56:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16:07:02</t>
+          <t>12:56:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16:07:02</t>
+          <t>12:56:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
